--- a/pipeline_output/WB_2W_H&M.xlsx
+++ b/pipeline_output/WB_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11124,12 +11124,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11612,12 +11612,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12227,12 +12227,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12598,12 +12598,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12842,12 +12842,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12959,12 +12959,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13193,12 +13193,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13691,12 +13691,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13935,12 +13935,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14296,12 +14296,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14540,12 +14540,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -15038,12 +15038,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15165,12 +15165,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15282,12 +15282,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15399,12 +15399,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15516,12 +15516,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15633,12 +15633,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15877,12 +15877,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16375,12 +16375,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16502,12 +16502,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16629,12 +16629,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16746,12 +16746,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16873,12 +16873,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -17000,12 +17000,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17117,12 +17117,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17371,12 +17371,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17488,12 +17488,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17615,12 +17615,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17742,12 +17742,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17869,12 +17869,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -18113,12 +18113,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18230,12 +18230,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18347,12 +18347,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18464,12 +18464,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18581,12 +18581,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18708,12 +18708,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18835,12 +18835,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18962,12 +18962,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19206,12 +19206,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19460,12 +19460,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19577,12 +19577,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19831,12 +19831,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19948,12 +19948,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -20075,12 +20075,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20202,12 +20202,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20319,12 +20319,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20446,12 +20446,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20573,12 +20573,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20700,12 +20700,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20827,12 +20827,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20944,12 +20944,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -21061,12 +21061,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21178,12 +21178,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21295,12 +21295,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21539,12 +21539,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21666,12 +21666,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21920,12 +21920,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -22037,12 +22037,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22164,12 +22164,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22408,12 +22408,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22535,12 +22535,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22662,12 +22662,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22779,12 +22779,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22906,12 +22906,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -23033,12 +23033,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23160,12 +23160,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23287,12 +23287,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23414,12 +23414,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23668,12 +23668,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23795,12 +23795,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23922,12 +23922,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -24049,12 +24049,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -24166,12 +24166,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -24283,12 +24283,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24400,12 +24400,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24517,12 +24517,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24634,12 +24634,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24751,12 +24751,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24868,12 +24868,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24985,12 +24985,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -25102,12 +25102,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -25219,12 +25219,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25336,12 +25336,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25687,12 +25687,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25804,12 +25804,12 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25921,12 +25921,12 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
